--- a/storage/app/templates/jsh/melting_check_sheet.xlsx
+++ b/storage/app/templates/jsh/melting_check_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\Docker-env\apps-laravel\aicc-mmcs\storage\app\templates\jsh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C526B0D3-C0CF-4EBB-8324-28903F149F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3A5CA7-345B-4572-ACFF-70FE0F625100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
   <si>
     <t>Halaman 1 / 1</t>
   </si>
@@ -398,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -447,6 +447,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -482,6 +510,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -501,9 +536,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -515,30 +547,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -853,141 +861,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="18" t="s">
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
     </row>
     <row r="2" spans="1:52" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="35" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="34" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="29" t="s">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="30"/>
-      <c r="X2" s="22" t="s">
+      <c r="W2" s="42"/>
+      <c r="X2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="24"/>
-      <c r="AA2" s="20" t="s">
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20" t="s">
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="22" t="s">
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="24"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="36"/>
     </row>
     <row r="3" spans="1:52" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="34" t="s">
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="29" t="s">
+      <c r="P3" s="49"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="30"/>
-      <c r="X3" s="22" t="s">
+      <c r="W3" s="42"/>
+      <c r="X3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
-      <c r="AF3" s="20"/>
-      <c r="AG3" s="20"/>
-      <c r="AH3" s="20"/>
-      <c r="AI3" s="20"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="32"/>
+      <c r="AF3" s="32"/>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
       <c r="AQ3" s="15"/>
       <c r="AR3" s="6"/>
       <c r="AS3" s="6"/>
@@ -1000,49 +1008,49 @@
       <c r="AZ3" s="9"/>
     </row>
     <row r="4" spans="1:52" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="34" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="45"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="47"/>
-      <c r="V4" s="29" t="s">
+      <c r="P4" s="49"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="30"/>
-      <c r="X4" s="20" t="s">
+      <c r="W4" s="42"/>
+      <c r="X4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="20"/>
-      <c r="AE4" s="20"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="20"/>
-      <c r="AH4" s="20"/>
-      <c r="AI4" s="20"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
       <c r="AQ4" s="16"/>
       <c r="AR4" s="8"/>
       <c r="AS4" s="8"/>
@@ -1055,43 +1063,43 @@
       <c r="AZ4" s="10"/>
     </row>
     <row r="5" spans="1:52" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
       <c r="S5" s="13"/>
       <c r="T5" s="13"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="41"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="55"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="21"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
-      <c r="AG5" s="21"/>
-      <c r="AH5" s="21"/>
-      <c r="AI5" s="21"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="33"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="33"/>
       <c r="AQ5" s="17"/>
       <c r="AR5" s="7"/>
       <c r="AS5" s="7"/>
@@ -1104,95 +1112,95 @@
       <c r="AZ5" s="11"/>
     </row>
     <row r="6" spans="1:52" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="38"/>
-      <c r="AE6" s="38"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="38"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="43"/>
+      <c r="AE6" s="43"/>
+      <c r="AF6" s="43"/>
+      <c r="AG6" s="43"/>
+      <c r="AH6" s="43"/>
+      <c r="AI6" s="43"/>
     </row>
     <row r="7" spans="1:52" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="27" t="s">
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="38"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:52" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="4">
         <v>1</v>
       </c>
@@ -1286,15 +1294,15 @@
       <c r="AH8" s="4">
         <v>31</v>
       </c>
-      <c r="AI8" s="48"/>
+      <c r="AI8" s="45"/>
       <c r="AN8" s="12"/>
     </row>
     <row r="9" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1330,7 +1338,7 @@
     </row>
     <row r="10" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="40" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1374,7 +1382,7 @@
     </row>
     <row r="11" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
-      <c r="B11" s="26"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1459,11 +1467,11 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1537,7 +1545,7 @@
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
       <c r="AI14" s="5">
-        <f t="shared" ref="AI14:AI30" si="0">SUM(D14:AH14)</f>
+        <f t="shared" ref="AI14:AI41" si="0">SUM(D14:AH14)</f>
         <v>0</v>
       </c>
     </row>
@@ -1761,977 +1769,980 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="49">
+    <row r="20" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="18">
         <v>7</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="51"/>
-      <c r="X20" s="51"/>
-      <c r="Y20" s="51"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="51"/>
-      <c r="AB20" s="51"/>
-      <c r="AC20" s="51"/>
-      <c r="AD20" s="51"/>
-      <c r="AE20" s="51"/>
-      <c r="AF20" s="51"/>
-      <c r="AG20" s="51"/>
-      <c r="AH20" s="51"/>
-      <c r="AI20" s="52">
+      <c r="B20" s="19"/>
+      <c r="C20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="20"/>
+      <c r="AH20" s="20"/>
+      <c r="AI20" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="49">
+    <row r="21" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="18">
         <v>8</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="51"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="51"/>
-      <c r="Z21" s="51"/>
-      <c r="AA21" s="51"/>
-      <c r="AB21" s="51"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="51"/>
-      <c r="AE21" s="51"/>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="51"/>
-      <c r="AH21" s="51"/>
-      <c r="AI21" s="52">
+      <c r="B21" s="19"/>
+      <c r="C21" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="49">
+    <row r="22" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="18">
         <v>9</v>
       </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="51"/>
-      <c r="X22" s="51"/>
-      <c r="Y22" s="51"/>
-      <c r="Z22" s="51"/>
-      <c r="AA22" s="51"/>
-      <c r="AB22" s="51"/>
-      <c r="AC22" s="51"/>
-      <c r="AD22" s="51"/>
-      <c r="AE22" s="51"/>
-      <c r="AF22" s="51"/>
-      <c r="AG22" s="51"/>
-      <c r="AH22" s="51"/>
-      <c r="AI22" s="52">
+      <c r="B22" s="19"/>
+      <c r="C22" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="20"/>
+      <c r="AH22" s="20"/>
+      <c r="AI22" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="49">
+    <row r="23" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="18">
         <v>10</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-      <c r="L23" s="51"/>
-      <c r="M23" s="51"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="51"/>
-      <c r="V23" s="51"/>
-      <c r="W23" s="51"/>
-      <c r="X23" s="51"/>
-      <c r="Y23" s="51"/>
-      <c r="Z23" s="51"/>
-      <c r="AA23" s="51"/>
-      <c r="AB23" s="51"/>
-      <c r="AC23" s="51"/>
-      <c r="AD23" s="51"/>
-      <c r="AE23" s="51"/>
-      <c r="AF23" s="51"/>
-      <c r="AG23" s="51"/>
-      <c r="AH23" s="51"/>
-      <c r="AI23" s="52">
+      <c r="B23" s="19"/>
+      <c r="C23" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
+      <c r="AG23" s="20"/>
+      <c r="AH23" s="20"/>
+      <c r="AI23" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="49">
+    <row r="24" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="18">
         <v>11</v>
       </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
-      <c r="W24" s="51"/>
-      <c r="X24" s="51"/>
-      <c r="Y24" s="51"/>
-      <c r="Z24" s="51"/>
-      <c r="AA24" s="51"/>
-      <c r="AB24" s="51"/>
-      <c r="AC24" s="51"/>
-      <c r="AD24" s="51"/>
-      <c r="AE24" s="51"/>
-      <c r="AF24" s="51"/>
-      <c r="AG24" s="51"/>
-      <c r="AH24" s="51"/>
-      <c r="AI24" s="52">
+      <c r="B24" s="19"/>
+      <c r="C24" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="20"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49">
+    <row r="25" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="18">
         <v>12</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-      <c r="L25" s="51"/>
-      <c r="M25" s="51"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="51"/>
-      <c r="S25" s="51"/>
-      <c r="T25" s="51"/>
-      <c r="U25" s="51"/>
-      <c r="V25" s="51"/>
-      <c r="W25" s="51"/>
-      <c r="X25" s="51"/>
-      <c r="Y25" s="51"/>
-      <c r="Z25" s="51"/>
-      <c r="AA25" s="51"/>
-      <c r="AB25" s="51"/>
-      <c r="AC25" s="51"/>
-      <c r="AD25" s="51"/>
-      <c r="AE25" s="51"/>
-      <c r="AF25" s="51"/>
-      <c r="AG25" s="51"/>
-      <c r="AH25" s="51"/>
-      <c r="AI25" s="52">
+      <c r="B25" s="19"/>
+      <c r="C25" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="20"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="20"/>
+      <c r="AG25" s="20"/>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="49">
+    <row r="26" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="18">
         <v>13</v>
       </c>
-      <c r="B26" s="50"/>
-      <c r="C26" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="51"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="51"/>
-      <c r="AA26" s="51"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="51"/>
-      <c r="AE26" s="51"/>
-      <c r="AF26" s="51"/>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="52">
+      <c r="B26" s="19"/>
+      <c r="C26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AD26" s="20"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="20"/>
+      <c r="AH26" s="20"/>
+      <c r="AI26" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="49">
+    <row r="27" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="18">
         <v>14</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="51"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="51"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="51"/>
-      <c r="AA27" s="51"/>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="51"/>
-      <c r="AE27" s="51"/>
-      <c r="AF27" s="51"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="52">
+      <c r="B27" s="19"/>
+      <c r="C27" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="20"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
+      <c r="AG27" s="20"/>
+      <c r="AH27" s="20"/>
+      <c r="AI27" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="49">
+    <row r="28" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="18">
         <v>15</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="51"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="52">
+      <c r="B28" s="19"/>
+      <c r="C28" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="20"/>
+      <c r="AD28" s="20"/>
+      <c r="AE28" s="20"/>
+      <c r="AF28" s="20"/>
+      <c r="AG28" s="20"/>
+      <c r="AH28" s="20"/>
+      <c r="AI28" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="49">
+    <row r="29" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="18">
         <v>16</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="51"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="51"/>
-      <c r="AA29" s="51"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="51"/>
-      <c r="AE29" s="51"/>
-      <c r="AF29" s="51"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="52">
+      <c r="B29" s="19"/>
+      <c r="C29" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AH29" s="20"/>
+      <c r="AI29" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:35" s="53" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="49">
+    <row r="30" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="18">
         <v>17</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="51"/>
-      <c r="W30" s="51"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="Z30" s="51"/>
-      <c r="AA30" s="51"/>
-      <c r="AB30" s="51"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="51"/>
-      <c r="AE30" s="51"/>
-      <c r="AF30" s="51"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="52">
+      <c r="B30" s="19"/>
+      <c r="C30" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="20"/>
+      <c r="AD30" s="20"/>
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
+      <c r="AG30" s="20"/>
+      <c r="AH30" s="20"/>
+      <c r="AI30" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="25" t="s">
+    <row r="31" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="18">
+        <v>18</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
+      <c r="AG31" s="20"/>
+      <c r="AH31" s="20"/>
+      <c r="AI31" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="18">
+        <v>19</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
+      <c r="AC32" s="20"/>
+      <c r="AD32" s="20"/>
+      <c r="AE32" s="20"/>
+      <c r="AF32" s="20"/>
+      <c r="AG32" s="20"/>
+      <c r="AH32" s="20"/>
+      <c r="AI32" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="18">
+        <v>20</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
+      <c r="AC33" s="20"/>
+      <c r="AD33" s="20"/>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="20"/>
+      <c r="AG33" s="20"/>
+      <c r="AH33" s="20"/>
+      <c r="AI33" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="18">
+        <v>21</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
+      <c r="AC34" s="20"/>
+      <c r="AD34" s="20"/>
+      <c r="AE34" s="20"/>
+      <c r="AF34" s="20"/>
+      <c r="AG34" s="20"/>
+      <c r="AH34" s="20"/>
+      <c r="AI34" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="18">
+        <v>22</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
+      <c r="Z35" s="20"/>
+      <c r="AA35" s="20"/>
+      <c r="AB35" s="20"/>
+      <c r="AC35" s="20"/>
+      <c r="AD35" s="20"/>
+      <c r="AE35" s="20"/>
+      <c r="AF35" s="20"/>
+      <c r="AG35" s="20"/>
+      <c r="AH35" s="20"/>
+      <c r="AI35" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="18">
+        <v>23</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
+      <c r="AC36" s="20"/>
+      <c r="AD36" s="20"/>
+      <c r="AE36" s="20"/>
+      <c r="AF36" s="20"/>
+      <c r="AG36" s="20"/>
+      <c r="AH36" s="20"/>
+      <c r="AI36" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="18">
+        <v>24</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20"/>
+      <c r="T37" s="20"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="20"/>
+      <c r="AE37" s="20"/>
+      <c r="AF37" s="20"/>
+      <c r="AG37" s="20"/>
+      <c r="AH37" s="20"/>
+      <c r="AI37" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="18">
+        <v>25</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
+      <c r="Q38" s="20"/>
+      <c r="R38" s="20"/>
+      <c r="S38" s="20"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="20"/>
+      <c r="AE38" s="20"/>
+      <c r="AF38" s="20"/>
+      <c r="AG38" s="20"/>
+      <c r="AH38" s="20"/>
+      <c r="AI38" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="18">
+        <v>26</v>
+      </c>
+      <c r="B39" s="19"/>
+      <c r="C39" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="20"/>
+      <c r="AE39" s="20"/>
+      <c r="AF39" s="20"/>
+      <c r="AG39" s="20"/>
+      <c r="AH39" s="20"/>
+      <c r="AI39" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="18">
+        <v>27</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="20"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="20"/>
+      <c r="AE40" s="20"/>
+      <c r="AF40" s="20"/>
+      <c r="AG40" s="20"/>
+      <c r="AH40" s="20"/>
+      <c r="AI40" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="18">
+        <v>28</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="20"/>
+      <c r="AE41" s="20"/>
+      <c r="AF41" s="20"/>
+      <c r="AG41" s="20"/>
+      <c r="AH41" s="20"/>
+      <c r="AI41" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="3"/>
-      <c r="AC31" s="3"/>
-      <c r="AD31" s="3"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="3"/>
-      <c r="AG31" s="3"/>
-      <c r="AH31" s="3"/>
-      <c r="AI31" s="3"/>
-    </row>
-    <row r="32" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <v>1</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-      <c r="AA32" s="3"/>
-      <c r="AB32" s="3"/>
-      <c r="AC32" s="3"/>
-      <c r="AD32" s="3"/>
-      <c r="AE32" s="3"/>
-      <c r="AF32" s="3"/>
-      <c r="AG32" s="3"/>
-      <c r="AH32" s="3"/>
-      <c r="AI32" s="5">
-        <f t="shared" ref="AI32:AI45" si="1">SUM(D32:AH32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <v>2</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
-      <c r="AC33" s="3"/>
-      <c r="AD33" s="3"/>
-      <c r="AE33" s="3"/>
-      <c r="AF33" s="3"/>
-      <c r="AG33" s="3"/>
-      <c r="AH33" s="3"/>
-      <c r="AI33" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <v>3</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
-      <c r="AC34" s="3"/>
-      <c r="AD34" s="3"/>
-      <c r="AE34" s="3"/>
-      <c r="AF34" s="3"/>
-      <c r="AG34" s="3"/>
-      <c r="AH34" s="3"/>
-      <c r="AI34" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <v>4</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-      <c r="AA35" s="3"/>
-      <c r="AB35" s="3"/>
-      <c r="AC35" s="3"/>
-      <c r="AD35" s="3"/>
-      <c r="AE35" s="3"/>
-      <c r="AF35" s="3"/>
-      <c r="AG35" s="3"/>
-      <c r="AH35" s="3"/>
-      <c r="AI35" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <v>5</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-      <c r="AA36" s="3"/>
-      <c r="AB36" s="3"/>
-      <c r="AC36" s="3"/>
-      <c r="AD36" s="3"/>
-      <c r="AE36" s="3"/>
-      <c r="AF36" s="3"/>
-      <c r="AG36" s="3"/>
-      <c r="AH36" s="3"/>
-      <c r="AI36" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <v>6</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-      <c r="AA37" s="3"/>
-      <c r="AB37" s="3"/>
-      <c r="AC37" s="3"/>
-      <c r="AD37" s="3"/>
-      <c r="AE37" s="3"/>
-      <c r="AF37" s="3"/>
-      <c r="AG37" s="3"/>
-      <c r="AH37" s="3"/>
-      <c r="AI37" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <v>7</v>
-      </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3"/>
-      <c r="AC38" s="3"/>
-      <c r="AD38" s="3"/>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="3"/>
-      <c r="AG38" s="3"/>
-      <c r="AH38" s="3"/>
-      <c r="AI38" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <v>8</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-      <c r="AG39" s="3"/>
-      <c r="AH39" s="3"/>
-      <c r="AI39" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
-        <v>9</v>
-      </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="3"/>
-      <c r="AG40" s="3"/>
-      <c r="AH40" s="3"/>
-      <c r="AI40" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
-        <v>10</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
-      <c r="AD41" s="3"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="3"/>
-      <c r="AG41" s="3"/>
-      <c r="AH41" s="3"/>
-      <c r="AI41" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
-        <v>11</v>
-      </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2763,14 +2774,11 @@
       <c r="AF42" s="3"/>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
-      <c r="AI42" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI42" s="3"/>
     </row>
     <row r="43" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="2" t="s">
@@ -2808,13 +2816,13 @@
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
       <c r="AI43" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AI43:AI60" si="1">SUM(D43:AH43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
@@ -2858,7 +2866,7 @@
     </row>
     <row r="45" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="s">
@@ -2901,10 +2909,10 @@
       </c>
     </row>
     <row r="46" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="26"/>
+      <c r="A46" s="2">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
         <v>28</v>
       </c>
@@ -2939,14 +2947,19 @@
       <c r="AF46" s="3"/>
       <c r="AG46" s="3"/>
       <c r="AH46" s="3"/>
-      <c r="AI46" s="3"/>
+      <c r="AI46" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="A47" s="2">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2978,16 +2991,18 @@
       <c r="AF47" s="3"/>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
+      <c r="AI47" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="48" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>1</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -3021,19 +3036,17 @@
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
       <c r="AI48" s="5">
-        <f>SUM(D48:AH48)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>2</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -3067,19 +3080,17 @@
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
       <c r="AI49" s="5">
-        <f>SUM(D49:AH49)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>3</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B50" s="1"/>
       <c r="C50" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -3113,17 +3124,15 @@
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
       <c r="AI50" s="5">
-        <f>SUM(D50:AH50)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>4</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
         <v>28</v>
       </c>
@@ -3159,17 +3168,15 @@
       <c r="AG51" s="3"/>
       <c r="AH51" s="3"/>
       <c r="AI51" s="5">
-        <f>SUM(D51:AH51)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
-        <v>5</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="2" t="s">
         <v>28</v>
       </c>
@@ -3205,16 +3212,18 @@
       <c r="AG52" s="3"/>
       <c r="AH52" s="3"/>
       <c r="AI52" s="5">
-        <f>SUM(D52:AH52)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+      <c r="A53" s="2">
+        <v>11</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3246,14 +3255,19 @@
       <c r="AF53" s="3"/>
       <c r="AG53" s="3"/>
       <c r="AH53" s="3"/>
-      <c r="AI53" s="3"/>
+      <c r="AI53" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
-      <c r="B54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="2"/>
+      <c r="A54" s="2">
+        <v>12</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3286,36 +3300,663 @@
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
       <c r="AI54" s="5">
-        <f>SUM(D54:AH54)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="26">
+        <v>13</v>
+      </c>
+      <c r="B55" s="25"/>
+      <c r="C55" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="24"/>
+      <c r="N55" s="24"/>
+      <c r="O55" s="24"/>
+      <c r="P55" s="24"/>
+      <c r="Q55" s="24"/>
+      <c r="R55" s="24"/>
+      <c r="S55" s="24"/>
+      <c r="T55" s="24"/>
+      <c r="U55" s="24"/>
+      <c r="V55" s="24"/>
+      <c r="W55" s="24"/>
+      <c r="X55" s="24"/>
+      <c r="Y55" s="24"/>
+      <c r="Z55" s="24"/>
+      <c r="AA55" s="24"/>
+      <c r="AB55" s="24"/>
+      <c r="AC55" s="24"/>
+      <c r="AD55" s="24"/>
+      <c r="AE55" s="24"/>
+      <c r="AF55" s="24"/>
+      <c r="AG55" s="24"/>
+      <c r="AH55" s="24"/>
+      <c r="AI55" s="5"/>
+    </row>
+    <row r="56" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="26">
+        <v>14</v>
+      </c>
+      <c r="B56" s="25"/>
+      <c r="C56" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="24"/>
+      <c r="N56" s="24"/>
+      <c r="O56" s="24"/>
+      <c r="P56" s="24"/>
+      <c r="Q56" s="24"/>
+      <c r="R56" s="24"/>
+      <c r="S56" s="24"/>
+      <c r="T56" s="24"/>
+      <c r="U56" s="24"/>
+      <c r="V56" s="24"/>
+      <c r="W56" s="24"/>
+      <c r="X56" s="24"/>
+      <c r="Y56" s="24"/>
+      <c r="Z56" s="24"/>
+      <c r="AA56" s="24"/>
+      <c r="AB56" s="24"/>
+      <c r="AC56" s="24"/>
+      <c r="AD56" s="24"/>
+      <c r="AE56" s="24"/>
+      <c r="AF56" s="24"/>
+      <c r="AG56" s="24"/>
+      <c r="AH56" s="24"/>
+      <c r="AI56" s="5"/>
+    </row>
+    <row r="57" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="26">
+        <v>15</v>
+      </c>
+      <c r="B57" s="25"/>
+      <c r="C57" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="24"/>
+      <c r="N57" s="24"/>
+      <c r="O57" s="24"/>
+      <c r="P57" s="24"/>
+      <c r="Q57" s="24"/>
+      <c r="R57" s="24"/>
+      <c r="S57" s="24"/>
+      <c r="T57" s="24"/>
+      <c r="U57" s="24"/>
+      <c r="V57" s="24"/>
+      <c r="W57" s="24"/>
+      <c r="X57" s="24"/>
+      <c r="Y57" s="24"/>
+      <c r="Z57" s="24"/>
+      <c r="AA57" s="24"/>
+      <c r="AB57" s="24"/>
+      <c r="AC57" s="24"/>
+      <c r="AD57" s="24"/>
+      <c r="AE57" s="24"/>
+      <c r="AF57" s="24"/>
+      <c r="AG57" s="24"/>
+      <c r="AH57" s="24"/>
+      <c r="AI57" s="5"/>
+    </row>
+    <row r="58" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="26">
+        <v>16</v>
+      </c>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="24"/>
+      <c r="N58" s="24"/>
+      <c r="O58" s="24"/>
+      <c r="P58" s="24"/>
+      <c r="Q58" s="24"/>
+      <c r="R58" s="24"/>
+      <c r="S58" s="24"/>
+      <c r="T58" s="24"/>
+      <c r="U58" s="24"/>
+      <c r="V58" s="24"/>
+      <c r="W58" s="24"/>
+      <c r="X58" s="24"/>
+      <c r="Y58" s="24"/>
+      <c r="Z58" s="24"/>
+      <c r="AA58" s="24"/>
+      <c r="AB58" s="24"/>
+      <c r="AC58" s="24"/>
+      <c r="AD58" s="24"/>
+      <c r="AE58" s="24"/>
+      <c r="AF58" s="24"/>
+      <c r="AG58" s="24"/>
+      <c r="AH58" s="24"/>
+      <c r="AI58" s="5"/>
+    </row>
+    <row r="59" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="26">
+        <v>17</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="26">
+        <v>18</v>
+      </c>
+      <c r="B60" s="1"/>
+      <c r="C60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="38"/>
+      <c r="C61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+    </row>
+    <row r="62" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+      <c r="AH62" s="3"/>
+    </row>
+    <row r="63" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>1</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+      <c r="AH63" s="3"/>
+      <c r="AI63" s="5">
+        <f>SUM(D63:AH63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>2</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3"/>
+      <c r="AH64" s="3"/>
+      <c r="AI64" s="5">
+        <f>SUM(D64:AH64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>3</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="R65" s="3"/>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
+      <c r="AH65" s="3"/>
+      <c r="AI65" s="5">
+        <f>SUM(D65:AH65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>4</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+      <c r="AH66" s="3"/>
+      <c r="AI66" s="5">
+        <f>SUM(D66:AH66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>5</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="5">
+        <f>SUM(D67:AH67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+      <c r="AH68" s="3"/>
+      <c r="AI68" s="3"/>
+    </row>
+    <row r="69" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="2"/>
+      <c r="B69" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+      <c r="U69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="3"/>
+      <c r="AD69" s="3"/>
+      <c r="AE69" s="3"/>
+      <c r="AF69" s="3"/>
+      <c r="AG69" s="3"/>
+      <c r="AH69" s="3"/>
+      <c r="AI69" s="5">
+        <f>SUM(D69:AH69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="81" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="82" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="83" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -3334,9 +3975,23 @@
     <row r="96" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="97" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="98" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="O2:Q2"/>
@@ -3352,11 +4007,10 @@
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="R2:U2"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="D7:AH7"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="B7:B8"/>
@@ -3364,10 +4018,11 @@
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="X4:Z4"/>
     <mergeCell ref="A6:AI6"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="R4:U4"/>
     <mergeCell ref="AA1:AI1"/>
     <mergeCell ref="AA2:AC2"/>
@@ -3376,6 +4031,7 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG3:AI5"/>
     <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="R3:U3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/storage/app/templates/jsh/melting_check_sheet.xlsx
+++ b/storage/app/templates/jsh/melting_check_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\Docker-env\apps-laravel\aicc-mmcs\storage\app\templates\jsh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3A5CA7-345B-4572-ACFF-70FE0F625100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7842F7-13EE-4E3D-A1A8-DAA9B8304D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
   <si>
     <t>Halaman 1 / 1</t>
   </si>
@@ -398,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -431,11 +431,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -447,23 +447,49 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -474,25 +500,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -504,11 +511,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -517,34 +521,10 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -849,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ113"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -861,141 +841,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="30" t="s">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="AB1" s="31"/>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="19"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
     </row>
     <row r="2" spans="1:52" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="50" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="49" t="s">
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="41" t="s">
+      <c r="P2" s="22"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="42"/>
-      <c r="X2" s="34" t="s">
+      <c r="W2" s="23"/>
+      <c r="X2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="32" t="s">
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32" t="s">
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="34" t="s">
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="36"/>
+      <c r="AH2" s="29"/>
+      <c r="AI2" s="30"/>
     </row>
     <row r="3" spans="1:52" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="49" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="41" t="s">
+      <c r="P3" s="22"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="42"/>
-      <c r="X3" s="34" t="s">
+      <c r="W3" s="23"/>
+      <c r="X3" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
-      <c r="AE3" s="32"/>
-      <c r="AF3" s="32"/>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
+      <c r="AE3" s="42"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
       <c r="AQ3" s="15"/>
       <c r="AR3" s="6"/>
       <c r="AS3" s="6"/>
@@ -1008,49 +988,49 @@
       <c r="AZ3" s="9"/>
     </row>
     <row r="4" spans="1:52" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="49" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="41" t="s">
+      <c r="P4" s="22"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="W4" s="42"/>
-      <c r="X4" s="32" t="s">
+      <c r="W4" s="23"/>
+      <c r="X4" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="32"/>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="32"/>
-      <c r="AD4" s="32"/>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="32"/>
-      <c r="AG4" s="32"/>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="32"/>
+      <c r="Y4" s="42"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="42"/>
+      <c r="AB4" s="42"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="42"/>
+      <c r="AE4" s="42"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="42"/>
+      <c r="AH4" s="42"/>
+      <c r="AI4" s="42"/>
       <c r="AQ4" s="16"/>
       <c r="AR4" s="8"/>
       <c r="AS4" s="8"/>
@@ -1063,43 +1043,43 @@
       <c r="AZ4" s="10"/>
     </row>
     <row r="5" spans="1:52" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
       <c r="O5" s="13"/>
       <c r="P5" s="13"/>
       <c r="Q5" s="13"/>
       <c r="R5" s="13"/>
       <c r="S5" s="13"/>
       <c r="T5" s="13"/>
-      <c r="U5" s="53"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="56"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="33"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
       <c r="AQ5" s="17"/>
       <c r="AR5" s="7"/>
       <c r="AS5" s="7"/>
@@ -1151,56 +1131,56 @@
       <c r="AI6" s="43"/>
     </row>
     <row r="7" spans="1:52" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="39" t="s">
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AA7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
+      <c r="AD7" s="39"/>
+      <c r="AE7" s="39"/>
+      <c r="AF7" s="39"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="40" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:52" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="4">
         <v>1</v>
       </c>
@@ -1298,11 +1278,11 @@
       <c r="AN8" s="12"/>
     </row>
     <row r="9" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1338,7 +1318,7 @@
     </row>
     <row r="10" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1382,7 +1362,7 @@
     </row>
     <row r="11" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
-      <c r="B11" s="38"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1467,11 +1447,11 @@
       </c>
     </row>
     <row r="13" spans="1:52" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1545,7 +1525,7 @@
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
       <c r="AI14" s="5">
-        <f t="shared" ref="AI14:AI41" si="0">SUM(D14:AH14)</f>
+        <f t="shared" ref="AI14:AI33" si="0">SUM(D14:AH14)</f>
         <v>0</v>
       </c>
     </row>
@@ -1769,980 +1749,977 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18">
+    <row r="20" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>7</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
-      <c r="AC20" s="20"/>
-      <c r="AD20" s="20"/>
-      <c r="AE20" s="20"/>
-      <c r="AF20" s="20"/>
-      <c r="AG20" s="20"/>
-      <c r="AH20" s="20"/>
-      <c r="AI20" s="21">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+      <c r="AH20" s="3"/>
+      <c r="AI20" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18">
+    <row r="21" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>8</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-      <c r="AF21" s="20"/>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
-      <c r="AI21" s="21">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="18">
+    <row r="22" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>9</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
-      <c r="AE22" s="20"/>
-      <c r="AF22" s="20"/>
-      <c r="AG22" s="20"/>
-      <c r="AH22" s="20"/>
-      <c r="AI22" s="21">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18">
+    <row r="23" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>10</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
-      <c r="AE23" s="20"/>
-      <c r="AF23" s="20"/>
-      <c r="AG23" s="20"/>
-      <c r="AH23" s="20"/>
-      <c r="AI23" s="21">
+      <c r="B23" s="1"/>
+      <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="18">
+    <row r="24" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>11</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
-      <c r="AE24" s="20"/>
-      <c r="AF24" s="20"/>
-      <c r="AG24" s="20"/>
-      <c r="AH24" s="20"/>
-      <c r="AI24" s="21">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="18">
+    <row r="25" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>12</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
-      <c r="AE25" s="20"/>
-      <c r="AF25" s="20"/>
-      <c r="AG25" s="20"/>
-      <c r="AH25" s="20"/>
-      <c r="AI25" s="21">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="18">
+    <row r="26" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>13</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
-      <c r="AE26" s="20"/>
-      <c r="AF26" s="20"/>
-      <c r="AG26" s="20"/>
-      <c r="AH26" s="20"/>
-      <c r="AI26" s="21">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="18">
+    <row r="27" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>14</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="20"/>
-      <c r="AF27" s="20"/>
-      <c r="AG27" s="20"/>
-      <c r="AH27" s="20"/>
-      <c r="AI27" s="21">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="18">
+    <row r="28" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>15</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
-      <c r="AE28" s="20"/>
-      <c r="AF28" s="20"/>
-      <c r="AG28" s="20"/>
-      <c r="AH28" s="20"/>
-      <c r="AI28" s="21">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="18">
+    <row r="29" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>16</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="20"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20"/>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
-      <c r="AC29" s="20"/>
-      <c r="AD29" s="20"/>
-      <c r="AE29" s="20"/>
-      <c r="AF29" s="20"/>
-      <c r="AG29" s="20"/>
-      <c r="AH29" s="20"/>
-      <c r="AI29" s="21">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="18">
+    <row r="30" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>17</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
-      <c r="AC30" s="20"/>
-      <c r="AD30" s="20"/>
-      <c r="AE30" s="20"/>
-      <c r="AF30" s="20"/>
-      <c r="AG30" s="20"/>
-      <c r="AH30" s="20"/>
-      <c r="AI30" s="21">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="18">
+    <row r="31" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>18</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20"/>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
-      <c r="AC31" s="20"/>
-      <c r="AD31" s="20"/>
-      <c r="AE31" s="20"/>
-      <c r="AF31" s="20"/>
-      <c r="AG31" s="20"/>
-      <c r="AH31" s="20"/>
-      <c r="AI31" s="21">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+      <c r="AH31" s="3"/>
+      <c r="AI31" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="18">
+    <row r="32" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>19</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
-      <c r="AC32" s="20"/>
-      <c r="AD32" s="20"/>
-      <c r="AE32" s="20"/>
-      <c r="AF32" s="20"/>
-      <c r="AG32" s="20"/>
-      <c r="AH32" s="20"/>
-      <c r="AI32" s="21">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+      <c r="AH32" s="3"/>
+      <c r="AI32" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="18">
+    <row r="33" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>20</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
-      <c r="AC33" s="20"/>
-      <c r="AD33" s="20"/>
-      <c r="AE33" s="20"/>
-      <c r="AF33" s="20"/>
-      <c r="AG33" s="20"/>
-      <c r="AH33" s="20"/>
-      <c r="AI33" s="21">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3"/>
+      <c r="AI33" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="18">
-        <v>21</v>
-      </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="20"/>
-      <c r="AC34" s="20"/>
-      <c r="AD34" s="20"/>
-      <c r="AE34" s="20"/>
-      <c r="AF34" s="20"/>
-      <c r="AG34" s="20"/>
-      <c r="AH34" s="20"/>
-      <c r="AI34" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="18">
-        <v>22</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20"/>
-      <c r="X35" s="20"/>
-      <c r="Y35" s="20"/>
-      <c r="Z35" s="20"/>
-      <c r="AA35" s="20"/>
-      <c r="AB35" s="20"/>
-      <c r="AC35" s="20"/>
-      <c r="AD35" s="20"/>
-      <c r="AE35" s="20"/>
-      <c r="AF35" s="20"/>
-      <c r="AG35" s="20"/>
-      <c r="AH35" s="20"/>
-      <c r="AI35" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="18">
-        <v>23</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="20"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
-      <c r="U36" s="20"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20"/>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="20"/>
-      <c r="AC36" s="20"/>
-      <c r="AD36" s="20"/>
-      <c r="AE36" s="20"/>
-      <c r="AF36" s="20"/>
-      <c r="AG36" s="20"/>
-      <c r="AH36" s="20"/>
-      <c r="AI36" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="18">
-        <v>24</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="20"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20"/>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="20"/>
-      <c r="AD37" s="20"/>
-      <c r="AE37" s="20"/>
-      <c r="AF37" s="20"/>
-      <c r="AG37" s="20"/>
-      <c r="AH37" s="20"/>
-      <c r="AI37" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="18">
-        <v>25</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-      <c r="W38" s="20"/>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="20"/>
-      <c r="AC38" s="20"/>
-      <c r="AD38" s="20"/>
-      <c r="AE38" s="20"/>
-      <c r="AF38" s="20"/>
-      <c r="AG38" s="20"/>
-      <c r="AH38" s="20"/>
-      <c r="AI38" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="18">
-        <v>26</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
-      <c r="P39" s="20"/>
-      <c r="Q39" s="20"/>
-      <c r="R39" s="20"/>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="20"/>
-      <c r="AA39" s="20"/>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="20"/>
-      <c r="AD39" s="20"/>
-      <c r="AE39" s="20"/>
-      <c r="AF39" s="20"/>
-      <c r="AG39" s="20"/>
-      <c r="AH39" s="20"/>
-      <c r="AI39" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="18">
-        <v>27</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="20"/>
-      <c r="O40" s="20"/>
-      <c r="P40" s="20"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="20"/>
-      <c r="T40" s="20"/>
-      <c r="U40" s="20"/>
-      <c r="V40" s="20"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40" s="20"/>
-      <c r="AB40" s="20"/>
-      <c r="AC40" s="20"/>
-      <c r="AD40" s="20"/>
-      <c r="AE40" s="20"/>
-      <c r="AF40" s="20"/>
-      <c r="AG40" s="20"/>
-      <c r="AH40" s="20"/>
-      <c r="AI40" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35" s="22" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="18">
-        <v>28</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
-      <c r="T41" s="20"/>
-      <c r="U41" s="20"/>
-      <c r="V41" s="20"/>
-      <c r="W41" s="20"/>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="20"/>
-      <c r="AA41" s="20"/>
-      <c r="AB41" s="20"/>
-      <c r="AC41" s="20"/>
-      <c r="AD41" s="20"/>
-      <c r="AE41" s="20"/>
-      <c r="AF41" s="20"/>
-      <c r="AG41" s="20"/>
-      <c r="AH41" s="20"/>
-      <c r="AI41" s="21">
-        <f t="shared" si="0"/>
+    <row r="34" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+      <c r="AH34" s="3"/>
+      <c r="AI34" s="3"/>
+    </row>
+    <row r="35" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3"/>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="5">
+        <f t="shared" ref="AI35:AI51" si="1">SUM(D35:AH35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>2</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+      <c r="AH36" s="3"/>
+      <c r="AI36" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>3</v>
+      </c>
+      <c r="B37" s="1"/>
+      <c r="C37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="3"/>
+      <c r="V37" s="3"/>
+      <c r="W37" s="3"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+      <c r="AH37" s="3"/>
+      <c r="AI37" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+      <c r="AH38" s="3"/>
+      <c r="AI38" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>6</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>7</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+      <c r="AH41" s="3"/>
+      <c r="AI41" s="5">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
+      <c r="A42" s="2">
+        <v>8</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -2774,11 +2751,14 @@
       <c r="AF42" s="3"/>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
-      <c r="AI42" s="3"/>
+      <c r="AI42" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="2" t="s">
@@ -2816,13 +2796,13 @@
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
       <c r="AI43" s="5">
-        <f t="shared" ref="AI43:AI60" si="1">SUM(D43:AH43)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
@@ -2866,7 +2846,7 @@
     </row>
     <row r="45" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B45" s="1"/>
       <c r="C45" s="2" t="s">
@@ -2910,7 +2890,7 @@
     </row>
     <row r="46" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
@@ -2954,7 +2934,7 @@
     </row>
     <row r="47" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="2" t="s">
@@ -2991,14 +2971,11 @@
       <c r="AF47" s="3"/>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
-      <c r="AI47" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI47" s="5"/>
     </row>
     <row r="48" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
@@ -3035,14 +3012,11 @@
       <c r="AF48" s="3"/>
       <c r="AG48" s="3"/>
       <c r="AH48" s="3"/>
-      <c r="AI48" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI48" s="5"/>
     </row>
     <row r="49" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="2" t="s">
@@ -3079,14 +3053,11 @@
       <c r="AF49" s="3"/>
       <c r="AG49" s="3"/>
       <c r="AH49" s="3"/>
-      <c r="AI49" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI49" s="5"/>
     </row>
     <row r="50" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="2" t="s">
@@ -3123,14 +3094,11 @@
       <c r="AF50" s="3"/>
       <c r="AG50" s="3"/>
       <c r="AH50" s="3"/>
-      <c r="AI50" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI50" s="5"/>
     </row>
     <row r="51" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
@@ -3173,10 +3141,10 @@
       </c>
     </row>
     <row r="52" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
-        <v>10</v>
-      </c>
-      <c r="B52" s="1"/>
+      <c r="A52" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="39"/>
       <c r="C52" s="2" t="s">
         <v>28</v>
       </c>
@@ -3211,19 +3179,14 @@
       <c r="AF52" s="3"/>
       <c r="AG52" s="3"/>
       <c r="AH52" s="3"/>
-      <c r="AI52" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI52" s="3"/>
     </row>
     <row r="53" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
-        <v>11</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A53" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3255,18 +3218,16 @@
       <c r="AF53" s="3"/>
       <c r="AG53" s="3"/>
       <c r="AH53" s="3"/>
-      <c r="AI53" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="54" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
-        <v>12</v>
-      </c>
-      <c r="B54" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="C54" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3300,182 +3261,200 @@
       <c r="AG54" s="3"/>
       <c r="AH54" s="3"/>
       <c r="AI54" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="26">
-        <v>13</v>
-      </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="24"/>
-      <c r="N55" s="24"/>
-      <c r="O55" s="24"/>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="24"/>
-      <c r="R55" s="24"/>
-      <c r="S55" s="24"/>
-      <c r="T55" s="24"/>
-      <c r="U55" s="24"/>
-      <c r="V55" s="24"/>
-      <c r="W55" s="24"/>
-      <c r="X55" s="24"/>
-      <c r="Y55" s="24"/>
-      <c r="Z55" s="24"/>
-      <c r="AA55" s="24"/>
-      <c r="AB55" s="24"/>
-      <c r="AC55" s="24"/>
-      <c r="AD55" s="24"/>
-      <c r="AE55" s="24"/>
-      <c r="AF55" s="24"/>
-      <c r="AG55" s="24"/>
-      <c r="AH55" s="24"/>
-      <c r="AI55" s="5"/>
-    </row>
-    <row r="56" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="26">
-        <v>14</v>
-      </c>
-      <c r="B56" s="25"/>
-      <c r="C56" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="24"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="24"/>
-      <c r="N56" s="24"/>
-      <c r="O56" s="24"/>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="24"/>
-      <c r="R56" s="24"/>
-      <c r="S56" s="24"/>
-      <c r="T56" s="24"/>
-      <c r="U56" s="24"/>
-      <c r="V56" s="24"/>
-      <c r="W56" s="24"/>
-      <c r="X56" s="24"/>
-      <c r="Y56" s="24"/>
-      <c r="Z56" s="24"/>
-      <c r="AA56" s="24"/>
-      <c r="AB56" s="24"/>
-      <c r="AC56" s="24"/>
-      <c r="AD56" s="24"/>
-      <c r="AE56" s="24"/>
-      <c r="AF56" s="24"/>
-      <c r="AG56" s="24"/>
-      <c r="AH56" s="24"/>
-      <c r="AI56" s="5"/>
-    </row>
-    <row r="57" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="26">
-        <v>15</v>
-      </c>
-      <c r="B57" s="25"/>
-      <c r="C57" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="24"/>
-      <c r="K57" s="24"/>
-      <c r="L57" s="24"/>
-      <c r="M57" s="24"/>
-      <c r="N57" s="24"/>
-      <c r="O57" s="24"/>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="24"/>
-      <c r="R57" s="24"/>
-      <c r="S57" s="24"/>
-      <c r="T57" s="24"/>
-      <c r="U57" s="24"/>
-      <c r="V57" s="24"/>
-      <c r="W57" s="24"/>
-      <c r="X57" s="24"/>
-      <c r="Y57" s="24"/>
-      <c r="Z57" s="24"/>
-      <c r="AA57" s="24"/>
-      <c r="AB57" s="24"/>
-      <c r="AC57" s="24"/>
-      <c r="AD57" s="24"/>
-      <c r="AE57" s="24"/>
-      <c r="AF57" s="24"/>
-      <c r="AG57" s="24"/>
-      <c r="AH57" s="24"/>
-      <c r="AI57" s="5"/>
-    </row>
-    <row r="58" spans="1:35" s="23" customFormat="1" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="26">
-        <v>16</v>
-      </c>
-      <c r="B58" s="25"/>
-      <c r="C58" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="24"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="24"/>
-      <c r="N58" s="24"/>
-      <c r="O58" s="24"/>
-      <c r="P58" s="24"/>
-      <c r="Q58" s="24"/>
-      <c r="R58" s="24"/>
-      <c r="S58" s="24"/>
-      <c r="T58" s="24"/>
-      <c r="U58" s="24"/>
-      <c r="V58" s="24"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="24"/>
-      <c r="Y58" s="24"/>
-      <c r="Z58" s="24"/>
-      <c r="AA58" s="24"/>
-      <c r="AB58" s="24"/>
-      <c r="AC58" s="24"/>
-      <c r="AD58" s="24"/>
-      <c r="AE58" s="24"/>
-      <c r="AF58" s="24"/>
-      <c r="AG58" s="24"/>
-      <c r="AH58" s="24"/>
-      <c r="AI58" s="5"/>
+        <f>SUM(D54:AH54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>2</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="5">
+        <f>SUM(D55:AH55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>3</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="5">
+        <f>SUM(D56:AH56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="3"/>
+      <c r="AI57" s="5">
+        <f>SUM(D57:AH57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>5</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="3"/>
+      <c r="AH58" s="3"/>
+      <c r="AI58" s="5">
+        <f>SUM(D58:AH58)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="26">
-        <v>17</v>
-      </c>
-      <c r="B59" s="1"/>
-      <c r="C59" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A59" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3507,19 +3486,14 @@
       <c r="AF59" s="3"/>
       <c r="AG59" s="3"/>
       <c r="AH59" s="3"/>
-      <c r="AI59" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="AI59" s="3"/>
     </row>
     <row r="60" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="26">
-        <v>18</v>
-      </c>
-      <c r="B60" s="1"/>
-      <c r="C60" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="A60" s="2"/>
+      <c r="B60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3552,411 +3526,30 @@
       <c r="AG60" s="3"/>
       <c r="AH60" s="3"/>
       <c r="AI60" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
-      <c r="AB61" s="3"/>
-      <c r="AC61" s="3"/>
-      <c r="AD61" s="3"/>
-      <c r="AE61" s="3"/>
-      <c r="AF61" s="3"/>
-      <c r="AG61" s="3"/>
-      <c r="AH61" s="3"/>
-      <c r="AI61" s="3"/>
-    </row>
-    <row r="62" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
-      <c r="AB62" s="3"/>
-      <c r="AC62" s="3"/>
-      <c r="AD62" s="3"/>
-      <c r="AE62" s="3"/>
-      <c r="AF62" s="3"/>
-      <c r="AG62" s="3"/>
-      <c r="AH62" s="3"/>
-    </row>
-    <row r="63" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="2">
-        <v>1</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
-      <c r="AB63" s="3"/>
-      <c r="AC63" s="3"/>
-      <c r="AD63" s="3"/>
-      <c r="AE63" s="3"/>
-      <c r="AF63" s="3"/>
-      <c r="AG63" s="3"/>
-      <c r="AH63" s="3"/>
-      <c r="AI63" s="5">
-        <f>SUM(D63:AH63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2">
-        <v>2</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
-      <c r="AB64" s="3"/>
-      <c r="AC64" s="3"/>
-      <c r="AD64" s="3"/>
-      <c r="AE64" s="3"/>
-      <c r="AF64" s="3"/>
-      <c r="AG64" s="3"/>
-      <c r="AH64" s="3"/>
-      <c r="AI64" s="5">
-        <f>SUM(D64:AH64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="2">
-        <v>3</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
-      <c r="AB65" s="3"/>
-      <c r="AC65" s="3"/>
-      <c r="AD65" s="3"/>
-      <c r="AE65" s="3"/>
-      <c r="AF65" s="3"/>
-      <c r="AG65" s="3"/>
-      <c r="AH65" s="3"/>
-      <c r="AI65" s="5">
-        <f>SUM(D65:AH65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="2">
-        <v>4</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
-      <c r="AB66" s="3"/>
-      <c r="AC66" s="3"/>
-      <c r="AD66" s="3"/>
-      <c r="AE66" s="3"/>
-      <c r="AF66" s="3"/>
-      <c r="AG66" s="3"/>
-      <c r="AH66" s="3"/>
-      <c r="AI66" s="5">
-        <f>SUM(D66:AH66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2">
-        <v>5</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
-      <c r="AB67" s="3"/>
-      <c r="AC67" s="3"/>
-      <c r="AD67" s="3"/>
-      <c r="AE67" s="3"/>
-      <c r="AF67" s="3"/>
-      <c r="AG67" s="3"/>
-      <c r="AH67" s="3"/>
-      <c r="AI67" s="5">
-        <f>SUM(D67:AH67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3"/>
-      <c r="AB68" s="3"/>
-      <c r="AC68" s="3"/>
-      <c r="AD68" s="3"/>
-      <c r="AE68" s="3"/>
-      <c r="AF68" s="3"/>
-      <c r="AG68" s="3"/>
-      <c r="AH68" s="3"/>
-      <c r="AI68" s="3"/>
-    </row>
-    <row r="69" spans="1:35" ht="13" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="2"/>
-      <c r="B69" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
-      <c r="AB69" s="3"/>
-      <c r="AC69" s="3"/>
-      <c r="AD69" s="3"/>
-      <c r="AE69" s="3"/>
-      <c r="AF69" s="3"/>
-      <c r="AG69" s="3"/>
-      <c r="AH69" s="3"/>
-      <c r="AI69" s="5">
-        <f>SUM(D69:AH69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+        <f>SUM(D60:AH60)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:35" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="81" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="82" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="83" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -3981,17 +3574,32 @@
     <row r="102" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="103" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="104" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="107" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="108" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="109" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="14" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="AA1:AI1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AA3:AC5"/>
+    <mergeCell ref="AD3:AF5"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="AG3:AI5"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="D7:AH7"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="A6:AI6"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="O2:Q2"/>
@@ -4007,31 +3615,7 @@
     <mergeCell ref="W5:Y5"/>
     <mergeCell ref="A2:C3"/>
     <mergeCell ref="R2:U2"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="D7:AH7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="A6:AI6"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="R4:U4"/>
-    <mergeCell ref="AA1:AI1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AA3:AC5"/>
-    <mergeCell ref="AD3:AF5"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="AG3:AI5"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="R3:U3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
